--- a/data/availability/projects/palm-hills-developments/hacienda-waters.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-waters.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -959,7 +959,6 @@
       <c r="G2" t="n">
         <v>374</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -970,7 +969,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -992,7 +991,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1016,7 +1015,6 @@
       <c r="G3" t="n">
         <v>374</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1027,7 +1025,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1049,7 +1047,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1073,7 +1071,6 @@
       <c r="G4" t="n">
         <v>374</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1084,7 +1081,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1106,7 +1103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1130,7 +1127,6 @@
       <c r="G5" t="n">
         <v>374</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1141,7 +1137,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1163,7 +1159,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1187,7 +1183,6 @@
       <c r="G6" t="n">
         <v>278</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1244,7 +1239,6 @@
       <c r="G7" t="n">
         <v>72.5</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1255,7 +1249,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1301,7 +1295,6 @@
       <c r="G8" t="n">
         <v>72.5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1312,7 +1305,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1358,7 +1351,6 @@
       <c r="G9" t="n">
         <v>72.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1369,7 +1361,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1415,7 +1407,6 @@
       <c r="G10" t="n">
         <v>72.5</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1426,7 +1417,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1472,7 +1463,6 @@
       <c r="G11" t="n">
         <v>72.5</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1483,7 +1473,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1529,7 +1519,6 @@
       <c r="G12" t="n">
         <v>141</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1540,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1586,7 +1575,6 @@
       <c r="G13" t="n">
         <v>141</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1597,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1643,7 +1631,6 @@
       <c r="G14" t="n">
         <v>141</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1654,7 +1641,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1700,7 +1687,6 @@
       <c r="G15" t="n">
         <v>141</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1711,7 +1697,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1757,7 +1743,6 @@
       <c r="G16" t="n">
         <v>141</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1768,7 +1753,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1814,7 +1799,6 @@
       <c r="G17" t="n">
         <v>141</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1825,7 +1809,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1871,7 +1855,6 @@
       <c r="G18" t="n">
         <v>141</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1882,7 +1865,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1928,7 +1911,6 @@
       <c r="G19" t="n">
         <v>141</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1939,7 +1921,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1985,7 +1967,6 @@
       <c r="G20" t="n">
         <v>141</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1996,7 +1977,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2042,7 +2023,6 @@
       <c r="G21" t="n">
         <v>141</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2053,7 +2033,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2099,7 +2079,6 @@
       <c r="G22" t="n">
         <v>141</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2110,7 +2089,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2156,7 +2135,6 @@
       <c r="G23" t="n">
         <v>141</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2167,7 +2145,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2213,7 +2191,6 @@
       <c r="G24" t="n">
         <v>141</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2224,7 +2201,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2270,7 +2247,6 @@
       <c r="G25" t="n">
         <v>141</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2281,7 +2257,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2327,7 +2303,6 @@
       <c r="G26" t="n">
         <v>141</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2338,7 +2313,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2384,7 +2359,6 @@
       <c r="G27" t="n">
         <v>141</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2395,7 +2369,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2441,7 +2415,6 @@
       <c r="G28" t="n">
         <v>141</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2452,7 +2425,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2498,7 +2471,6 @@
       <c r="G29" t="n">
         <v>141</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2509,7 +2481,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2555,7 +2527,6 @@
       <c r="G30" t="n">
         <v>141</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2566,7 +2537,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2612,7 +2583,6 @@
       <c r="G31" t="n">
         <v>141</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2623,7 +2593,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2669,7 +2639,6 @@
       <c r="G32" t="n">
         <v>141</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2680,7 +2649,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2726,7 +2695,6 @@
       <c r="G33" t="n">
         <v>141</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2737,7 +2705,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2783,7 +2751,6 @@
       <c r="G34" t="n">
         <v>141</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2794,7 +2761,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2840,7 +2807,6 @@
       <c r="G35" t="n">
         <v>141</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2851,7 +2817,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2897,7 +2863,6 @@
       <c r="G36" t="n">
         <v>141</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2908,7 +2873,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2954,7 +2919,6 @@
       <c r="G37" t="n">
         <v>151</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2965,7 +2929,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3011,7 +2975,6 @@
       <c r="G38" t="n">
         <v>141</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3022,7 +2985,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3068,7 +3031,6 @@
       <c r="G39" t="n">
         <v>141</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3079,7 +3041,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3125,7 +3087,6 @@
       <c r="G40" t="n">
         <v>141</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3136,7 +3097,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3182,7 +3143,6 @@
       <c r="G41" t="n">
         <v>141</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3193,7 +3153,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3239,7 +3199,6 @@
       <c r="G42" t="n">
         <v>141</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3250,7 +3209,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3296,7 +3255,6 @@
       <c r="G43" t="n">
         <v>141</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3307,7 +3265,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3353,7 +3311,6 @@
       <c r="G44" t="n">
         <v>141</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3364,7 +3321,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3410,7 +3367,6 @@
       <c r="G45" t="n">
         <v>151</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3421,7 +3377,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3467,7 +3423,6 @@
       <c r="G46" t="n">
         <v>72.5</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3478,7 +3433,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3524,7 +3479,6 @@
       <c r="G47" t="n">
         <v>72.5</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3535,7 +3489,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3581,7 +3535,6 @@
       <c r="G48" t="n">
         <v>72.5</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3592,7 +3545,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3638,7 +3591,6 @@
       <c r="G49" t="n">
         <v>72.5</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3649,7 +3601,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3695,7 +3647,6 @@
       <c r="G50" t="n">
         <v>72.5</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3706,7 +3657,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3752,7 +3703,6 @@
       <c r="G51" t="n">
         <v>72.5</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3763,7 +3713,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3809,7 +3759,6 @@
       <c r="G52" t="n">
         <v>72.5</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3820,7 +3769,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3866,7 +3815,6 @@
       <c r="G53" t="n">
         <v>72.5</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3877,7 +3825,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3923,7 +3871,6 @@
       <c r="G54" t="n">
         <v>72.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3934,7 +3881,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3980,7 +3927,6 @@
       <c r="G55" t="n">
         <v>72.5</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3991,7 +3937,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4037,7 +3983,6 @@
       <c r="G56" t="n">
         <v>72.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4048,7 +3993,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4094,7 +4039,6 @@
       <c r="G57" t="n">
         <v>72.5</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4105,7 +4049,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4151,7 +4095,6 @@
       <c r="G58" t="n">
         <v>72.5</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4162,7 +4105,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4208,7 +4151,6 @@
       <c r="G59" t="n">
         <v>114</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4219,7 +4161,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4265,7 +4207,6 @@
       <c r="G60" t="n">
         <v>72.5</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4276,7 +4217,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4322,7 +4263,6 @@
       <c r="G61" t="n">
         <v>114</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4333,7 +4273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4379,7 +4319,6 @@
       <c r="G62" t="n">
         <v>72.5</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4390,7 +4329,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4436,7 +4375,6 @@
       <c r="G63" t="n">
         <v>72.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4447,7 +4385,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4493,7 +4431,6 @@
       <c r="G64" t="n">
         <v>72.5</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4504,7 +4441,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4550,7 +4487,6 @@
       <c r="G65" t="n">
         <v>72.5</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4561,7 +4497,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4607,7 +4543,6 @@
       <c r="G66" t="n">
         <v>114</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4618,7 +4553,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4664,7 +4599,6 @@
       <c r="G67" t="n">
         <v>114</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4675,7 +4609,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4721,7 +4655,6 @@
       <c r="G68" t="n">
         <v>72.5</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4732,7 +4665,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4778,7 +4711,6 @@
       <c r="G69" t="n">
         <v>72.5</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4789,7 +4721,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4835,7 +4767,6 @@
       <c r="G70" t="n">
         <v>114</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4846,7 +4777,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4892,7 +4823,6 @@
       <c r="G71" t="n">
         <v>72.5</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4903,7 +4833,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4949,7 +4879,6 @@
       <c r="G72" t="n">
         <v>72.5</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4960,7 +4889,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5006,7 +4935,6 @@
       <c r="G73" t="n">
         <v>114</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5017,7 +4945,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5063,7 +4991,6 @@
       <c r="G74" t="n">
         <v>72.5</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5074,7 +5001,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5120,7 +5047,6 @@
       <c r="G75" t="n">
         <v>114</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5131,7 +5057,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5177,7 +5103,6 @@
       <c r="G76" t="n">
         <v>72.5</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5188,7 +5113,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5234,7 +5159,6 @@
       <c r="G77" t="n">
         <v>72.5</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5245,7 +5169,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5291,7 +5215,6 @@
       <c r="G78" t="n">
         <v>114</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5302,7 +5225,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5348,7 +5271,6 @@
       <c r="G79" t="n">
         <v>72.5</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5359,7 +5281,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5405,7 +5327,6 @@
       <c r="G80" t="n">
         <v>114</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5416,7 +5337,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5462,7 +5383,6 @@
       <c r="G81" t="n">
         <v>72.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5473,7 +5393,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5519,7 +5439,6 @@
       <c r="G82" t="n">
         <v>72.5</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5530,7 +5449,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5576,7 +5495,6 @@
       <c r="G83" t="n">
         <v>114</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5587,7 +5505,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5633,7 +5551,6 @@
       <c r="G84" t="n">
         <v>72.5</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5644,7 +5561,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5690,7 +5607,6 @@
       <c r="G85" t="n">
         <v>72.5</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5701,7 +5617,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5747,7 +5663,6 @@
       <c r="G86" t="n">
         <v>114</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5758,7 +5673,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5804,7 +5719,6 @@
       <c r="G87" t="n">
         <v>72.5</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5815,7 +5729,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5861,7 +5775,6 @@
       <c r="G88" t="n">
         <v>72.5</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5872,7 +5785,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5918,7 +5831,6 @@
       <c r="G89" t="n">
         <v>72.5</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5929,7 +5841,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5975,7 +5887,6 @@
       <c r="G90" t="n">
         <v>72.5</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5986,7 +5897,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6032,7 +5943,6 @@
       <c r="G91" t="n">
         <v>114</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6043,7 +5953,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6089,7 +5999,6 @@
       <c r="G92" t="n">
         <v>72.5</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6100,7 +6009,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6146,7 +6055,6 @@
       <c r="G93" t="n">
         <v>114</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6157,7 +6065,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6203,7 +6111,6 @@
       <c r="G94" t="n">
         <v>72.5</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6214,7 +6121,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6260,7 +6167,6 @@
       <c r="G95" t="n">
         <v>72.5</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6271,7 +6177,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6317,7 +6223,6 @@
       <c r="G96" t="n">
         <v>114</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6328,7 +6233,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6374,7 +6279,6 @@
       <c r="G97" t="n">
         <v>72.5</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6385,7 +6289,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6431,7 +6335,6 @@
       <c r="G98" t="n">
         <v>72.5</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6442,7 +6345,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6488,7 +6391,6 @@
       <c r="G99" t="n">
         <v>114</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6499,7 +6401,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6545,7 +6447,6 @@
       <c r="G100" t="n">
         <v>114</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6556,7 +6457,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6602,7 +6503,6 @@
       <c r="G101" t="n">
         <v>72.5</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6613,7 +6513,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6659,7 +6559,6 @@
       <c r="G102" t="n">
         <v>72.5</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6670,7 +6569,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6716,7 +6615,6 @@
       <c r="G103" t="n">
         <v>114</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6727,7 +6625,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6773,7 +6671,6 @@
       <c r="G104" t="n">
         <v>72.5</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6784,7 +6681,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6830,7 +6727,6 @@
       <c r="G105" t="n">
         <v>72.5</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6841,7 +6737,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6887,7 +6783,6 @@
       <c r="G106" t="n">
         <v>114</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6898,7 +6793,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6944,7 +6839,6 @@
       <c r="G107" t="n">
         <v>72.5</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6955,7 +6849,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7001,7 +6895,6 @@
       <c r="G108" t="n">
         <v>72.5</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7012,7 +6905,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7058,7 +6951,6 @@
       <c r="G109" t="n">
         <v>114</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7069,7 +6961,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7115,7 +7007,6 @@
       <c r="G110" t="n">
         <v>72.5</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7126,7 +7017,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7172,7 +7063,6 @@
       <c r="G111" t="n">
         <v>72.5</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7183,7 +7073,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7229,7 +7119,6 @@
       <c r="G112" t="n">
         <v>114</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7240,7 +7129,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7286,7 +7175,6 @@
       <c r="G113" t="n">
         <v>106</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7297,7 +7185,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7343,7 +7231,6 @@
       <c r="G114" t="n">
         <v>114</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7354,7 +7241,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7400,7 +7287,6 @@
       <c r="G115" t="n">
         <v>72.5</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7411,7 +7297,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7457,7 +7343,6 @@
       <c r="G116" t="n">
         <v>72.5</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7468,7 +7353,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7514,7 +7399,6 @@
       <c r="G117" t="n">
         <v>114</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7525,7 +7409,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7571,7 +7455,6 @@
       <c r="G118" t="n">
         <v>114</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7582,7 +7465,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7628,7 +7511,6 @@
       <c r="G119" t="n">
         <v>72.5</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7639,7 +7521,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7685,7 +7567,6 @@
       <c r="G120" t="n">
         <v>72.5</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7696,7 +7577,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7742,7 +7623,6 @@
       <c r="G121" t="n">
         <v>114</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7753,7 +7633,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7799,7 +7679,6 @@
       <c r="G122" t="n">
         <v>114</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7810,7 +7689,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7856,7 +7735,6 @@
       <c r="G123" t="n">
         <v>72.5</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7867,7 +7745,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7913,7 +7791,6 @@
       <c r="G124" t="n">
         <v>72.5</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7924,7 +7801,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7970,7 +7847,6 @@
       <c r="G125" t="n">
         <v>114</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7981,7 +7857,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8027,7 +7903,6 @@
       <c r="G126" t="n">
         <v>114</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8038,7 +7913,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8084,7 +7959,6 @@
       <c r="G127" t="n">
         <v>72.5</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8095,7 +7969,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8141,7 +8015,6 @@
       <c r="G128" t="n">
         <v>72.5</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8152,7 +8025,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8198,7 +8071,6 @@
       <c r="G129" t="n">
         <v>114</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8209,7 +8081,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8255,7 +8127,6 @@
       <c r="G130" t="n">
         <v>65</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8266,7 +8137,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8312,7 +8183,6 @@
       <c r="G131" t="n">
         <v>106</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8323,7 +8193,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8369,7 +8239,6 @@
       <c r="G132" t="n">
         <v>145</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8380,7 +8249,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8426,7 +8295,6 @@
       <c r="G133" t="n">
         <v>103</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8437,7 +8305,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8483,7 +8351,6 @@
       <c r="G134" t="n">
         <v>107</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8494,7 +8361,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8540,7 +8407,6 @@
       <c r="G135" t="n">
         <v>103</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8551,7 +8417,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8597,7 +8463,6 @@
       <c r="G136" t="n">
         <v>107</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8608,7 +8473,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8654,7 +8519,6 @@
       <c r="G137" t="n">
         <v>103</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8665,7 +8529,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8711,7 +8575,6 @@
       <c r="G138" t="n">
         <v>107</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8722,7 +8585,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8768,7 +8631,6 @@
       <c r="G139" t="n">
         <v>145</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8779,7 +8641,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8825,7 +8687,6 @@
       <c r="G140" t="n">
         <v>145</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8836,7 +8697,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8882,7 +8743,6 @@
       <c r="G141" t="n">
         <v>103</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8893,7 +8753,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8939,7 +8799,6 @@
       <c r="G142" t="n">
         <v>103</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8950,7 +8809,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8972,7 +8831,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8996,7 +8855,6 @@
       <c r="G143" t="n">
         <v>45.5</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9029,7 +8887,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9053,7 +8911,6 @@
       <c r="G144" t="n">
         <v>45.5</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9086,7 +8943,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9110,7 +8967,6 @@
       <c r="G145" t="n">
         <v>45.5</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9143,7 +8999,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9167,7 +9023,6 @@
       <c r="G146" t="n">
         <v>45.5</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9200,7 +9055,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9224,7 +9079,6 @@
       <c r="G147" t="n">
         <v>45.5</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9257,7 +9111,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9281,7 +9135,6 @@
       <c r="G148" t="n">
         <v>45.5</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9314,7 +9167,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9338,7 +9191,6 @@
       <c r="G149" t="n">
         <v>45.5</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9371,7 +9223,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9395,7 +9247,6 @@
       <c r="G150" t="n">
         <v>45.5</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9428,7 +9279,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9452,7 +9303,6 @@
       <c r="G151" t="n">
         <v>45.5</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9485,7 +9335,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9509,7 +9359,6 @@
       <c r="G152" t="n">
         <v>45.5</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9542,7 +9391,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9566,7 +9415,6 @@
       <c r="G153" t="n">
         <v>45.5</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9599,7 +9447,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9623,7 +9471,6 @@
       <c r="G154" t="n">
         <v>45.5</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9656,7 +9503,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9680,7 +9527,6 @@
       <c r="G155" t="n">
         <v>45.5</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9713,7 +9559,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9737,7 +9583,6 @@
       <c r="G156" t="n">
         <v>45.5</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9770,7 +9615,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9794,7 +9639,6 @@
       <c r="G157" t="n">
         <v>45.5</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9827,7 +9671,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9851,7 +9695,6 @@
       <c r="G158" t="n">
         <v>45.5</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9884,7 +9727,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9908,7 +9751,6 @@
       <c r="G159" t="n">
         <v>41.5</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9941,7 +9783,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9965,7 +9807,6 @@
       <c r="G160" t="n">
         <v>41.5</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9998,7 +9839,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10022,7 +9863,6 @@
       <c r="G161" t="n">
         <v>41.5</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10055,7 +9895,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10079,7 +9919,6 @@
       <c r="G162" t="n">
         <v>41.5</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10112,7 +9951,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10136,7 +9975,6 @@
       <c r="G163" t="n">
         <v>41.5</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10169,7 +10007,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10193,7 +10031,6 @@
       <c r="G164" t="n">
         <v>41.5</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10226,7 +10063,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10250,7 +10087,6 @@
       <c r="G165" t="n">
         <v>41.5</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10283,7 +10119,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10307,7 +10143,6 @@
       <c r="G166" t="n">
         <v>41.5</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10340,7 +10175,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10364,7 +10199,6 @@
       <c r="G167" t="n">
         <v>41.5</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10397,7 +10231,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10421,7 +10255,6 @@
       <c r="G168" t="n">
         <v>41.5</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10454,7 +10287,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10478,7 +10311,6 @@
       <c r="G169" t="n">
         <v>41.5</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10511,7 +10343,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10535,7 +10367,6 @@
       <c r="G170" t="n">
         <v>41.5</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10568,7 +10399,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10592,7 +10423,6 @@
       <c r="G171" t="n">
         <v>41.5</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10625,7 +10455,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10649,7 +10479,6 @@
       <c r="G172" t="n">
         <v>41.5</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10682,7 +10511,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10706,7 +10535,6 @@
       <c r="G173" t="n">
         <v>41.5</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10739,7 +10567,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10763,7 +10591,6 @@
       <c r="G174" t="n">
         <v>41.5</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10796,7 +10623,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10820,7 +10647,6 @@
       <c r="G175" t="n">
         <v>41.5</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10853,7 +10679,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10877,7 +10703,6 @@
       <c r="G176" t="n">
         <v>41.5</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10910,7 +10735,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10934,7 +10759,6 @@
       <c r="G177" t="n">
         <v>41.5</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10967,7 +10791,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10991,7 +10815,6 @@
       <c r="G178" t="n">
         <v>41.5</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11024,7 +10847,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11048,7 +10871,6 @@
       <c r="G179" t="n">
         <v>41.5</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11081,7 +10903,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11105,7 +10927,6 @@
       <c r="G180" t="n">
         <v>41.5</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11138,7 +10959,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11162,7 +10983,6 @@
       <c r="G181" t="n">
         <v>41.5</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11195,7 +11015,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11219,7 +11039,6 @@
       <c r="G182" t="n">
         <v>41.5</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11252,7 +11071,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11276,7 +11095,6 @@
       <c r="G183" t="n">
         <v>41.5</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11309,7 +11127,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11333,7 +11151,6 @@
       <c r="G184" t="n">
         <v>41.5</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11366,7 +11183,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11390,7 +11207,6 @@
       <c r="G185" t="n">
         <v>41.5</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11423,7 +11239,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11447,7 +11263,6 @@
       <c r="G186" t="n">
         <v>41.5</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11480,7 +11295,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11504,7 +11319,6 @@
       <c r="G187" t="n">
         <v>41.5</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11537,7 +11351,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11561,7 +11375,6 @@
       <c r="G188" t="n">
         <v>41.5</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11594,7 +11407,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11618,7 +11431,6 @@
       <c r="G189" t="n">
         <v>41.5</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11651,7 +11463,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11675,7 +11487,6 @@
       <c r="G190" t="n">
         <v>41.5</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11708,7 +11519,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11732,7 +11543,6 @@
       <c r="G191" t="n">
         <v>41.5</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11765,7 +11575,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11789,7 +11599,6 @@
       <c r="G192" t="n">
         <v>41.5</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11822,7 +11631,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11846,7 +11655,6 @@
       <c r="G193" t="n">
         <v>41.5</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11879,7 +11687,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11903,7 +11711,6 @@
       <c r="G194" t="n">
         <v>41.5</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11936,7 +11743,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11960,7 +11767,6 @@
       <c r="G195" t="n">
         <v>41.5</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11993,7 +11799,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12017,7 +11823,6 @@
       <c r="G196" t="n">
         <v>41.5</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12050,7 +11855,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12074,7 +11879,6 @@
       <c r="G197" t="n">
         <v>41.5</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12107,7 +11911,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12131,7 +11935,6 @@
       <c r="G198" t="n">
         <v>41.5</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12164,7 +11967,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12188,7 +11991,6 @@
       <c r="G199" t="n">
         <v>41.5</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12221,7 +12023,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12245,7 +12047,6 @@
       <c r="G200" t="n">
         <v>41.5</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12278,7 +12079,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12302,7 +12103,6 @@
       <c r="G201" t="n">
         <v>41.5</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12335,7 +12135,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12359,7 +12159,6 @@
       <c r="G202" t="n">
         <v>41.5</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12392,7 +12191,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12416,7 +12215,6 @@
       <c r="G203" t="n">
         <v>41.5</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12449,7 +12247,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12473,7 +12271,6 @@
       <c r="G204" t="n">
         <v>41.5</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12506,7 +12303,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12530,7 +12327,6 @@
       <c r="G205" t="n">
         <v>41.5</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12563,7 +12359,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12587,7 +12383,6 @@
       <c r="G206" t="n">
         <v>41.5</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12620,7 +12415,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12644,7 +12439,6 @@
       <c r="G207" t="n">
         <v>41.5</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12677,7 +12471,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12701,7 +12495,6 @@
       <c r="G208" t="n">
         <v>41.5</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12734,7 +12527,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12758,7 +12551,6 @@
       <c r="G209" t="n">
         <v>41.5</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12791,7 +12583,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12815,7 +12607,6 @@
       <c r="G210" t="n">
         <v>41.5</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12848,7 +12639,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12872,7 +12663,6 @@
       <c r="G211" t="n">
         <v>41.5</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12905,7 +12695,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12929,7 +12719,6 @@
       <c r="G212" t="n">
         <v>41.5</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12962,7 +12751,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12986,7 +12775,6 @@
       <c r="G213" t="n">
         <v>41.5</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13019,7 +12807,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Cabins</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13043,7 +12831,6 @@
       <c r="G214" t="n">
         <v>41.5</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
